--- a/BOM/blackbody_a.xlsx
+++ b/BOM/blackbody_a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanya\Documents\LHR\blackbodies v1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73215B20-DCF7-4281-8F1B-8B8798F66EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB1ED0-253E-450F-A883-5B2228EDDE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{1255D6DC-D857-485F-AEA4-F2BE1B407C3F}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{1255D6DC-D857-485F-AEA4-F2BE1B407C3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Full BOM" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
   <si>
     <t>Reference</t>
   </si>
@@ -365,14 +365,26 @@
     <t>ABM3-8.000MHZ-D2Y-T</t>
   </si>
   <si>
-    <t>DS04-254-1S-01BK</t>
+    <t>CAN Protection TVS Diode</t>
+  </si>
+  <si>
+    <t>LEDs</t>
+  </si>
+  <si>
+    <t>D3, D4, D5, D7, D8, D11, D12, CAN_LED</t>
+  </si>
+  <si>
+    <t>SW5, SW6</t>
+  </si>
+  <si>
+    <t>Button</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,6 +518,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="33">
@@ -849,11 +866,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1850,13 +1868,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE6EB85-2D41-4A0F-BD2C-E1EF59CBA94E}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="33.59765625" customWidth="1"/>
-    <col min="2" max="2" width="28.19921875" customWidth="1"/>
-    <col min="3" max="3" width="6.53125" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.53125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.06640625" style="1"/>
+    <col min="4" max="4" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -1889,265 +1908,169 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1053091102</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1" t="s">
         <v>110</v>
       </c>
     </row>
